--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
   </si>
   <si>
     <t>ТубаКСУВХ1</t>
@@ -101,8 +98,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -188,11 +186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -200,9 +199,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,20 +555,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46156</v>
       </c>
       <c r="B2">
         <v>1911</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
       <c r="F2">
         <v>5.032</v>
@@ -587,7 +586,7 @@
         <v>7.75</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -597,80 +596,80 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
         <v>5.032</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>1.5103</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="6">
         <v>7.6</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <v>7.75</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>0.15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8">
         <v>5.032</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>1</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8">
         <v>7.6</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>7.75</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>0.15</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -146,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,12 +156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -212,17 +206,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,49 +46,37 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
+    <t>Варна</t>
   </si>
   <si>
     <t>В8972ВР</t>
   </si>
   <si>
+    <t>В7580ТЕ</t>
+  </si>
+  <si>
     <t>В3018ХЕ</t>
   </si>
   <si>
     <t>78970155027721343</t>
   </si>
   <si>
+    <t>78970155027721335</t>
+  </si>
+  <si>
     <t>78970155027721350</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:37:00</t>
-  </si>
-  <si>
-    <t>10:55:00</t>
-  </si>
-  <si>
-    <t>3232047798 3232047798</t>
-  </si>
-  <si>
-    <t>3232094815 3232094815</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -511,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +505,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,195 +546,258 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>29.83</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H2">
+        <v>21.18</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J2">
+        <v>21.48</v>
+      </c>
+      <c r="K2">
+        <v>104940</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>8.02</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H3">
+        <v>12.27</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>12.51</v>
+      </c>
+      <c r="K3">
+        <v>104940</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>69.62</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H4">
+        <v>112.09</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J4">
+        <v>114.18</v>
+      </c>
+      <c r="K4">
+        <v>13912</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>37.97</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H5">
+        <v>59.61</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J5">
+        <v>60.75</v>
+      </c>
+      <c r="K5">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7">
+        <v>107.59</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.5959</v>
+      </c>
+      <c r="E10" s="7">
+        <v>171.7</v>
+      </c>
+      <c r="F10" s="7">
+        <v>174.93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7">
+        <v>29.83</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.71</v>
+      </c>
+      <c r="E11" s="7">
+        <v>21.18</v>
+      </c>
+      <c r="F11" s="7">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>27.29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2">
-        <v>0.78</v>
-      </c>
-      <c r="I2" s="1">
-        <v>21.29</v>
-      </c>
-      <c r="J2">
-        <v>0.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>21.56</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>104550</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>49.46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1.72</v>
-      </c>
-      <c r="I3" s="1">
-        <v>85.06999999999999</v>
-      </c>
-      <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>86.56</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>162580</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
+      <c r="B12" s="7">
+        <v>8.02</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1.5299</v>
+      </c>
+      <c r="E12" s="7">
+        <v>12.27</v>
+      </c>
+      <c r="F12" s="7">
+        <v>12.51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7">
-        <v>49.46</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.72</v>
-      </c>
-      <c r="E8" s="7">
-        <v>85.06999999999999</v>
-      </c>
-      <c r="F8" s="7">
-        <v>86.56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>27.29</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.7801</v>
-      </c>
-      <c r="E9" s="7">
-        <v>21.29</v>
-      </c>
-      <c r="F9" s="7">
-        <v>21.56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="10">
-        <v>76.75</v>
-      </c>
-      <c r="C10" s="10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>106.36</v>
-      </c>
-      <c r="F10" s="10">
-        <v>108.12</v>
+      <c r="B13" s="10">
+        <v>145.44</v>
+      </c>
+      <c r="C13" s="10">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>205.15</v>
+      </c>
+      <c r="F13" s="10">
+        <v>208.92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -46,10 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>В8972ВР</t>
@@ -77,6 +86,18 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>13:23</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -496,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,10 +530,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -546,22 +569,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46182</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>29.83</v>
@@ -578,25 +607,31 @@
       <c r="J2">
         <v>21.48</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
         <v>104940</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>114641</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46182</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>8.02</v>
@@ -613,25 +648,31 @@
       <c r="J3">
         <v>12.51</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3">
         <v>104940</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>114643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46182</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>69.62</v>
@@ -648,25 +689,31 @@
       <c r="J4">
         <v>114.18</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
         <v>13912</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>114792</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46188</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>37.97</v>
@@ -683,13 +730,19 @@
       <c r="J5">
         <v>60.75</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5">
         <v>1632</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M5">
+        <v>275422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -697,18 +750,18 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>7</v>
@@ -717,9 +770,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B10" s="7">
         <v>107.59</v>
@@ -737,9 +790,9 @@
         <v>174.93</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" s="7">
         <v>29.83</v>
@@ -757,9 +810,9 @@
         <v>21.48</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
         <v>8.02</v>
@@ -777,9 +830,9 @@
         <v>12.51</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B13" s="10">
         <v>145.44</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -49,55 +49,31 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>ТубаКСУВХ1</t>
   </si>
   <si>
     <t>В8972ВР</t>
   </si>
   <si>
-    <t>В7580ТЕ</t>
-  </si>
-  <si>
-    <t>В3018ХЕ</t>
+    <t>78970155027721368</t>
   </si>
   <si>
     <t>78970155027721343</t>
   </si>
   <si>
-    <t>78970155027721335</t>
-  </si>
-  <si>
-    <t>78970155027721350</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:23</t>
+    <t>2026-06-19 09:01:31</t>
+  </si>
+  <si>
+    <t>2026-06-24 08:43:13</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -517,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,12 +506,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,288 +543,168 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="H2">
+        <v>7.55</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="J2">
+        <v>7.7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>28.3</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>18.4</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>18.68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>29.83</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H2">
-        <v>21.18</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J2">
-        <v>21.48</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L2">
-        <v>104940</v>
-      </c>
-      <c r="M2">
-        <v>114641</v>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>8.02</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H3">
-        <v>12.27</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J3">
-        <v>12.51</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7">
+        <v>28.3</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.6502</v>
+      </c>
+      <c r="E8" s="7">
+        <v>18.4</v>
+      </c>
+      <c r="F8" s="7">
+        <v>18.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="E9" s="7">
+        <v>7.55</v>
+      </c>
+      <c r="F9" s="7">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L3">
-        <v>104940</v>
-      </c>
-      <c r="M3">
-        <v>114643</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>69.62</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="H4">
-        <v>112.09</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="J4">
-        <v>114.18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4">
-        <v>13912</v>
-      </c>
-      <c r="M4">
-        <v>114792</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46188</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>37.97</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="H5">
-        <v>59.61</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J5">
-        <v>60.75</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5">
-        <v>1632</v>
-      </c>
-      <c r="M5">
-        <v>275422</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="7">
-        <v>107.59</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="10">
+        <v>33.3</v>
+      </c>
+      <c r="C10" s="10">
         <v>2</v>
       </c>
-      <c r="D10" s="8">
-        <v>1.5959</v>
-      </c>
-      <c r="E10" s="7">
-        <v>171.7</v>
-      </c>
-      <c r="F10" s="7">
-        <v>174.93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="7">
-        <v>29.83</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.71</v>
-      </c>
-      <c r="E11" s="7">
-        <v>21.18</v>
-      </c>
-      <c r="F11" s="7">
-        <v>21.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7">
-        <v>8.02</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1.5299</v>
-      </c>
-      <c r="E12" s="7">
-        <v>12.27</v>
-      </c>
-      <c r="F12" s="7">
-        <v>12.51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="10">
-        <v>145.44</v>
-      </c>
-      <c r="C13" s="10">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>205.15</v>
-      </c>
-      <c r="F13" s="10">
-        <v>208.92</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>25.95</v>
+      </c>
+      <c r="F10" s="10">
+        <v>26.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>ТубаКСУВХ1</t>
@@ -70,10 +79,19 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-19 09:01:31</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:43:13</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:01:00</t>
+  </si>
+  <si>
+    <t>08:42:00</t>
+  </si>
+  <si>
+    <t>3233572665 3233572665</t>
+  </si>
+  <si>
+    <t>3233805116 3233805116</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -502,14 +520,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,80 +564,107 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>1.51</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>7.55</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.54</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>7.7</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46197</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>28.3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
         <v>0.65</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>18.4</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>18.68</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>105290</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -624,29 +672,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7">
         <v>28.3</v>
@@ -664,9 +712,9 @@
         <v>18.68</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>5</v>
@@ -684,9 +732,9 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B10" s="10">
         <v>33.3</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1911 O5 Варна</t>
+    <t>Варна</t>
   </si>
   <si>
     <t>ТубаКСУВХ1</t>
@@ -79,19 +76,10 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:01:00</t>
-  </si>
-  <si>
-    <t>08:42:00</t>
-  </si>
-  <si>
-    <t>3233572665 3233572665</t>
-  </si>
-  <si>
-    <t>3233805116 3233805116</t>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>08:43</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -511,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +508,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,101 +557,92 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
+      <c r="G2" s="1">
+        <v>1.51</v>
       </c>
       <c r="H2">
-        <v>1.51</v>
+        <v>7.55</v>
       </c>
       <c r="I2" s="1">
-        <v>7.55</v>
+        <v>1.54</v>
       </c>
       <c r="J2">
-        <v>1.54</v>
-      </c>
-      <c r="K2" s="1">
         <v>7.7</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
+        <v>118329</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46197</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>28.3</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>18.4</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>18.68</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>18.4</v>
-      </c>
-      <c r="J3">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>18.68</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
+      <c r="L3">
+        <v>105290</v>
       </c>
       <c r="M3">
-        <v>105290</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
+        <v>202488</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -672,29 +650,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7">
         <v>28.3</v>
@@ -712,9 +690,9 @@
         <v>18.68</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7">
         <v>5</v>
@@ -732,9 +710,9 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B10" s="10">
         <v>33.3</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,31 +55,64 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>В8972ВР</t>
   </si>
   <si>
-    <t>В3018ХЕ</t>
+    <t>ТубаКСУВХ1</t>
+  </si>
+  <si>
+    <t>В7580ТЕ</t>
   </si>
   <si>
     <t>78970155027721343</t>
   </si>
   <si>
-    <t>78970155027721350</t>
+    <t>78970155027721368</t>
+  </si>
+  <si>
+    <t>78970155027721335</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-06 08:37:47</t>
-  </si>
-  <si>
-    <t>2026-07-10 10:49:31</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:47:00</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>08:37:00</t>
+  </si>
+  <si>
+    <t>10:42:00</t>
+  </si>
+  <si>
+    <t>3234860345 3234860345</t>
+  </si>
+  <si>
+    <t>3235174457 3235174457</t>
+  </si>
+  <si>
+    <t>3235183025 3235183025</t>
+  </si>
+  <si>
+    <t>3235523598 3235523598</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -496,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,15 +541,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -550,174 +588,300 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>31.86</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>19.75</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>20.07</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>105930</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>6.33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <v>1.51</v>
+      </c>
+      <c r="I3" s="1">
+        <v>9.56</v>
+      </c>
+      <c r="J3">
+        <v>1.54</v>
+      </c>
+      <c r="K3" s="1">
+        <v>9.75</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>23.91</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
+        <v>1.51</v>
+      </c>
+      <c r="I4" s="1">
+        <v>36.1</v>
+      </c>
+      <c r="J4">
+        <v>1.54</v>
+      </c>
+      <c r="K4" s="1">
+        <v>36.82</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>106030</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>29.95</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H2">
-        <v>18.57</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J2">
-        <v>18.87</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2">
-        <v>105580</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46213</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>44.96</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>68.34</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>69.69</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="L3">
-        <v>164040</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>67.98</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
+        <v>1.73</v>
+      </c>
+      <c r="I5" s="1">
+        <v>117.61</v>
+      </c>
+      <c r="J5">
+        <v>1.76</v>
+      </c>
+      <c r="K5" s="1">
+        <v>119.64</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>14572</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="7">
+        <v>67.98</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.7301</v>
+      </c>
+      <c r="E10" s="7">
+        <v>117.61</v>
+      </c>
+      <c r="F10" s="7">
+        <v>119.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
+      <c r="B11" s="7">
+        <v>31.86</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.6199</v>
+      </c>
+      <c r="E11" s="7">
+        <v>19.75</v>
+      </c>
+      <c r="F11" s="7">
+        <v>20.07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
-        <v>44.96</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E8" s="7">
-        <v>68.34</v>
-      </c>
-      <c r="F8" s="7">
-        <v>69.69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7">
-        <v>29.95</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="E9" s="7">
-        <v>18.57</v>
-      </c>
-      <c r="F9" s="7">
-        <v>18.87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="10">
-        <v>74.91</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B12" s="7">
+        <v>30.24</v>
+      </c>
+      <c r="C12" s="7">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>86.91</v>
-      </c>
-      <c r="F10" s="10">
-        <v>88.56</v>
+      <c r="D12" s="8">
+        <v>1.5099</v>
+      </c>
+      <c r="E12" s="7">
+        <v>45.66</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="10">
+        <v>130.08</v>
+      </c>
+      <c r="C13" s="10">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>183.02</v>
+      </c>
+      <c r="F13" s="10">
+        <v>186.28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -140,7 +140,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="8">
-        <v>1.7301</v>
+        <v>1.730068</v>
       </c>
       <c r="E10" s="7">
         <v>117.61</v>
@@ -852,7 +852,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="8">
-        <v>1.5099</v>
+        <v>1.509921</v>
       </c>
       <c r="E12" s="7">
         <v>45.66</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -532,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -545,13 +548,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -594,186 +597,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>31.86</v>
+        <v>31.857</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
-        <v>19.75</v>
-      </c>
       <c r="J2">
+        <v>19.75134</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
-        <v>20.07</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>20.06991</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2">
         <v>105930</v>
       </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>6.33</v>
+        <v>6.331</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3">
+        <v>1.401</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.51</v>
       </c>
-      <c r="I3" s="1">
-        <v>9.56</v>
-      </c>
       <c r="J3">
+        <v>9.559810000000001</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.54</v>
       </c>
-      <c r="K3" s="1">
-        <v>9.75</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>9.749739999999999</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46225</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>23.91</v>
+        <v>23.909</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4">
+        <v>1.401</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.51</v>
       </c>
-      <c r="I4" s="1">
-        <v>36.1</v>
-      </c>
       <c r="J4">
+        <v>36.10259</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.54</v>
       </c>
-      <c r="K4" s="1">
-        <v>36.82</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>36.81986</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4">
         <v>106030</v>
       </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46232</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>67.98</v>
+        <v>67.977</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5">
+        <v>1.674</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.73</v>
       </c>
-      <c r="I5" s="1">
-        <v>117.61</v>
-      </c>
       <c r="J5">
+        <v>117.60021</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.76</v>
       </c>
-      <c r="K5" s="1">
-        <v>119.64</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>119.63952</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5">
         <v>14572</v>
       </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -781,58 +799,58 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7">
-        <v>67.98</v>
+        <v>67.977</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="8">
-        <v>1.730068</v>
+        <v>1.73</v>
       </c>
       <c r="E10" s="7">
-        <v>117.61</v>
+        <v>117.6</v>
       </c>
       <c r="F10" s="7">
         <v>119.64</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="7">
-        <v>31.86</v>
+        <v>31.857</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="8">
-        <v>0.6199</v>
+        <v>0.62</v>
       </c>
       <c r="E11" s="7">
         <v>19.75</v>
@@ -841,9 +859,9 @@
         <v>20.07</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="7">
         <v>30.24</v>
@@ -852,7 +870,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="8">
-        <v>1.509921</v>
+        <v>1.51</v>
       </c>
       <c r="E12" s="7">
         <v>45.66</v>
@@ -861,19 +879,19 @@
         <v>46.57</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="10">
-        <v>130.08</v>
+        <v>130.074</v>
       </c>
       <c r="C13" s="10">
         <v>4</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>183.02</v>
+        <v>183.01</v>
       </c>
       <c r="F13" s="10">
         <v>186.28</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -141,9 +138,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -237,10 +234,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,13 +545,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,201 +594,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>31.857</v>
       </c>
       <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>19.751</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>20.07</v>
+      </c>
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>19.75134</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>20.06991</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>105930</v>
       </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>6.331</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I3" s="1">
-        <v>1.51</v>
+        <v>9.56</v>
       </c>
       <c r="J3">
-        <v>9.559810000000001</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>9.749739999999999</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3">
+        <v>9.75</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46225</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>23.909</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I4" s="1">
-        <v>1.51</v>
+        <v>36.103</v>
       </c>
       <c r="J4">
-        <v>36.10259</v>
+        <v>1.54</v>
       </c>
       <c r="K4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L4" s="1">
-        <v>36.81986</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4">
+        <v>36.82</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
         <v>106030</v>
       </c>
-      <c r="O4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46232</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>67.977</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I5" s="1">
-        <v>1.73</v>
+        <v>117.6</v>
       </c>
       <c r="J5">
-        <v>117.60021</v>
+        <v>1.76</v>
       </c>
       <c r="K5" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L5" s="1">
-        <v>119.63952</v>
-      </c>
-      <c r="M5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5">
+        <v>119.64</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
         <v>14572</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -799,89 +781,89 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="7">
         <v>67.977</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>1</v>
       </c>
       <c r="D10" s="8">
         <v>1.73</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>117.6</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>119.64</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="7">
         <v>31.857</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>1</v>
       </c>
       <c r="D11" s="8">
         <v>0.62</v>
       </c>
-      <c r="E11" s="7">
-        <v>19.75</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="8">
+        <v>19.751</v>
+      </c>
+      <c r="F11" s="8">
         <v>20.07</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
         <v>30.24</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>2</v>
       </c>
       <c r="D12" s="8">
         <v>1.51</v>
       </c>
-      <c r="E12" s="7">
-        <v>45.66</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="8">
+        <v>45.663</v>
+      </c>
+      <c r="F12" s="8">
         <v>46.57</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="10">
         <v>130.074</v>
@@ -891,7 +873,7 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>183.01</v>
+        <v>183.014</v>
       </c>
       <c r="F13" s="10">
         <v>186.28</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,61 +55,34 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1911 O5 Варна</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>В8972ВР</t>
   </si>
   <si>
-    <t>ТубаКСУВХ1</t>
-  </si>
-  <si>
-    <t>В7580ТЕ</t>
+    <t>В3018ХЕ</t>
   </si>
   <si>
     <t>78970155027721343</t>
   </si>
   <si>
-    <t>78970155027721368</t>
-  </si>
-  <si>
-    <t>78970155027721335</t>
+    <t>78970155027721350</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>08:47:00</t>
-  </si>
-  <si>
-    <t>08:40:00</t>
-  </si>
-  <si>
-    <t>08:37:00</t>
-  </si>
-  <si>
-    <t>10:42:00</t>
-  </si>
-  <si>
-    <t>3234860345 3234860345</t>
-  </si>
-  <si>
-    <t>3235174457 3235174457</t>
-  </si>
-  <si>
-    <t>3235183025 3235183025</t>
-  </si>
-  <si>
-    <t>3235523598 3235523598</t>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>12:52</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -138,9 +108,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -234,10 +204,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -541,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,57 +560,51 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>27.138</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H2">
+        <v>17.368</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="J2">
+        <v>17.64</v>
+      </c>
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>31.857</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>0.62</v>
-      </c>
-      <c r="I2" s="1">
-        <v>19.751</v>
-      </c>
-      <c r="J2">
-        <v>0.63</v>
-      </c>
-      <c r="K2" s="1">
-        <v>20.07</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
+      <c r="L2">
+        <v>106217</v>
       </c>
       <c r="M2">
-        <v>105930</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
+        <v>140336</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46225</v>
+        <v>46237</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -650,238 +613,127 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>41.011</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="H3">
+        <v>72.179</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="J3">
+        <v>73.41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>164710</v>
+      </c>
+      <c r="M3">
+        <v>231900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7">
+        <v>41.011</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1.75999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="F8" s="7">
+        <v>73.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>6.331</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.51</v>
-      </c>
-      <c r="I3" s="1">
-        <v>9.56</v>
-      </c>
-      <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
-        <v>9.75</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
+      <c r="B9" s="7">
+        <v>27.138</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.6399899999999999</v>
+      </c>
+      <c r="E9" s="7">
+        <v>17.37</v>
+      </c>
+      <c r="F9" s="7">
+        <v>17.64</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46225</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>23.909</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>1.51</v>
-      </c>
-      <c r="I4" s="1">
-        <v>36.103</v>
-      </c>
-      <c r="J4">
-        <v>1.54</v>
-      </c>
-      <c r="K4" s="1">
-        <v>36.82</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>106030</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46232</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>67.977</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>1.73</v>
-      </c>
-      <c r="I5" s="1">
-        <v>117.6</v>
-      </c>
-      <c r="J5">
-        <v>1.76</v>
-      </c>
-      <c r="K5" s="1">
-        <v>119.64</v>
-      </c>
-      <c r="L5" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="M5">
-        <v>14572</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="7">
-        <v>67.977</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.73</v>
-      </c>
-      <c r="E10" s="8">
-        <v>117.6</v>
-      </c>
-      <c r="F10" s="8">
-        <v>119.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="7">
-        <v>31.857</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="8">
-        <v>19.751</v>
-      </c>
-      <c r="F11" s="8">
-        <v>20.07</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7">
-        <v>30.24</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B10" s="10">
+        <v>68.149</v>
+      </c>
+      <c r="C10" s="10">
         <v>2</v>
       </c>
-      <c r="D12" s="8">
-        <v>1.51</v>
-      </c>
-      <c r="E12" s="8">
-        <v>45.663</v>
-      </c>
-      <c r="F12" s="8">
-        <v>46.57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="10">
-        <v>130.074</v>
-      </c>
-      <c r="C13" s="10">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>183.014</v>
-      </c>
-      <c r="F13" s="10">
-        <v>186.28</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>89.55</v>
+      </c>
+      <c r="F10" s="10">
+        <v>91.05</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,10 +58,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>В8972ВР</t>
@@ -79,10 +79,19 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>12:52</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>09:22:00</t>
+  </si>
+  <si>
+    <t>3236507393 3236507393</t>
+  </si>
+  <si>
+    <t>3236860709 3236860709</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
@@ -107,10 +116,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -190,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -204,10 +214,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,16 +523,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,13 +573,16 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -578,33 +594,36 @@
         <v>19</v>
       </c>
       <c r="F2">
-        <v>27.138</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H2">
-        <v>17.368</v>
+        <v>28.17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
       </c>
       <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>17.64</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>106217</v>
+        <v>27.888</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>18.592</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
       </c>
       <c r="M2">
-        <v>140336</v>
+        <v>106515</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -619,33 +638,36 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>41.011</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H3">
-        <v>72.179</v>
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.708</v>
       </c>
       <c r="I3" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J3">
-        <v>73.41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>164710</v>
+        <v>81.98399999999999</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K3" s="1">
+        <v>88.8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>231900</v>
+        <v>165335</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -653,82 +675,82 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="7">
-        <v>41.011</v>
-      </c>
-      <c r="C8" s="7">
+        <v>48</v>
+      </c>
+      <c r="C8" s="8">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
-        <v>1.75999</v>
+      <c r="D8" s="9">
+        <v>1.708</v>
       </c>
       <c r="E8" s="7">
-        <v>72.18000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F8" s="7">
-        <v>73.41</v>
+        <v>88.8</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="7">
-        <v>27.138</v>
-      </c>
-      <c r="C9" s="7">
+        <v>28.17</v>
+      </c>
+      <c r="C9" s="8">
         <v>1</v>
       </c>
-      <c r="D9" s="8">
-        <v>0.6399899999999999</v>
+      <c r="D9" s="9">
+        <v>0.98999</v>
       </c>
       <c r="E9" s="7">
-        <v>17.37</v>
+        <v>27.89</v>
       </c>
       <c r="F9" s="7">
-        <v>17.64</v>
+        <v>18.59</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="10">
-        <v>68.149</v>
-      </c>
-      <c r="C10" s="10">
+    <row r="10" spans="1:14">
+      <c r="A10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="11">
+        <v>76.17</v>
+      </c>
+      <c r="C10" s="12">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>89.55</v>
-      </c>
-      <c r="F10" s="10">
-        <v>91.05</v>
+      <c r="D10" s="9"/>
+      <c r="E10" s="11">
+        <v>109.87</v>
+      </c>
+      <c r="F10" s="11">
+        <v>107.39</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ/КСУВХ ГЕРГАНА ДСХ И ДПЛФУ.xlsx
@@ -600,10 +600,10 @@
         <v>21</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>27.888</v>
+        <v>18.31</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -644,10 +644,10 @@
         <v>21</v>
       </c>
       <c r="H3" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I3" s="1">
-        <v>81.98399999999999</v>
+        <v>87.36</v>
       </c>
       <c r="J3" s="1">
         <v>1.85</v>
@@ -706,10 +706,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="9">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="E8" s="7">
-        <v>81.98</v>
+        <v>87.36</v>
       </c>
       <c r="F8" s="7">
         <v>88.8</v>
@@ -726,10 +726,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="9">
-        <v>0.98999</v>
+        <v>0.64998</v>
       </c>
       <c r="E9" s="7">
-        <v>27.89</v>
+        <v>18.31</v>
       </c>
       <c r="F9" s="7">
         <v>18.59</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="11">
-        <v>109.87</v>
+        <v>105.67</v>
       </c>
       <c r="F10" s="11">
         <v>107.39</v>
